--- a/data/trans_orig/P74B-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P74B-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su pareja percibe algún tipo de pensión en 2007</t>
+          <t>Población según si su pareja percibe algún tipo de pensión en 2007 (tasa de respuesta: 98,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20322</t>
+          <t>20246</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>40768</t>
+          <t>40541</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>113854</t>
+          <t>114532</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>130767</t>
+          <t>131087</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>78,46%</t>
+          <t>78,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>132791</t>
+          <t>134684</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>172382</t>
+          <t>174844</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>37,18%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>284377</t>
+          <t>284604</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>304823</t>
+          <t>304899</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14348</t>
+          <t>14028</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31261</t>
+          <t>30583</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>297878</t>
+          <t>295416</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>337469</t>
+          <t>335576</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,34%</t>
+          <t>62,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,76%</t>
+          <t>71,36%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24685</t>
+          <t>25409</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>48360</t>
+          <t>48290</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>132636</t>
+          <t>131506</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>150953</t>
+          <t>150412</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>79,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>154759</t>
+          <t>154964</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>200410</t>
+          <t>199332</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,45%</t>
+          <t>33,27%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>384860</t>
+          <t>384930</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>408535</t>
+          <t>407811</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>14990</t>
+          <t>15531</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>33307</t>
+          <t>34437</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>398753</t>
+          <t>399831</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>444404</t>
+          <t>444199</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,55%</t>
+          <t>66,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>74,14%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>9188</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24412</t>
+          <t>25823</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>86589</t>
+          <t>87329</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>104262</t>
+          <t>104462</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>71,14%</t>
+          <t>71,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>85,66%</t>
+          <t>85,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>95153</t>
+          <t>95359</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>130617</t>
+          <t>130561</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>29,82%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>291643</t>
+          <t>290232</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>306996</t>
+          <t>306867</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17449</t>
+          <t>17249</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>35122</t>
+          <t>34382</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>307149</t>
+          <t>307205</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>342613</t>
+          <t>342407</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>70,16%</t>
+          <t>70,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,26%</t>
+          <t>78,22%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18598</t>
+          <t>18572</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38918</t>
+          <t>37826</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>133128</t>
+          <t>133937</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>155241</t>
+          <t>154323</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>74,25%</t>
+          <t>74,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>151249</t>
+          <t>150148</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>192973</t>
+          <t>191879</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>36,87%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>302173</t>
+          <t>303265</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>322493</t>
+          <t>322519</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>88,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>24067</t>
+          <t>24985</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>46180</t>
+          <t>45371</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>327426</t>
+          <t>328520</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>369150</t>
+          <t>370251</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,92%</t>
+          <t>63,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,94%</t>
+          <t>71,15%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>87757</t>
+          <t>87341</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>128470</t>
+          <t>128270</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>488369</t>
+          <t>487602</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>524803</t>
+          <t>524709</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>79,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>85,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>574679</t>
+          <t>573623</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>654034</t>
+          <t>658317</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>32,47%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1287042</t>
+          <t>1287242</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1327755</t>
+          <t>1328171</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>87273</t>
+          <t>87367</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>123707</t>
+          <t>124474</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1373554</t>
+          <t>1369271</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1452909</t>
+          <t>1453965</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,74%</t>
+          <t>67,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>71,71%</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2484,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su pareja percibe algún tipo de pensión en 2012</t>
+          <t>Población según si su pareja percibe algún tipo de pensión en 2012 (tasa de respuesta: 97,38%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>36402</t>
+          <t>35222</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>63289</t>
+          <t>62037</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>102107</t>
+          <t>102792</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>130825</t>
+          <t>129761</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>53,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>67,59%</t>
+          <t>67,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>143705</t>
+          <t>142285</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>189098</t>
+          <t>187982</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,26%</t>
+          <t>38,03%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>237408</t>
+          <t>238660</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>264295</t>
+          <t>265475</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>79,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>62719</t>
+          <t>63783</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>91437</t>
+          <t>90752</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>46,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>305144</t>
+          <t>306260</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>350537</t>
+          <t>351957</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>61,74%</t>
+          <t>61,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>70,92%</t>
+          <t>71,21%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37324</t>
+          <t>38803</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>67456</t>
+          <t>68013</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>165116</t>
+          <t>165514</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>198348</t>
+          <t>199179</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>59,31%</t>
+          <t>59,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>71,24%</t>
+          <t>71,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>210761</t>
+          <t>210108</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>263305</t>
+          <t>261281</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,94%</t>
+          <t>37,65%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>348078</t>
+          <t>347521</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>378210</t>
+          <t>376731</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,77%</t>
+          <t>83,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>80066</t>
+          <t>79235</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>113298</t>
+          <t>112900</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>40,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>430643</t>
+          <t>432667</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>483187</t>
+          <t>483840</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,06%</t>
+          <t>62,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,63%</t>
+          <t>69,72%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19627</t>
+          <t>21904</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44004</t>
+          <t>45400</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>118197</t>
+          <t>118516</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>146040</t>
+          <t>144955</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>60,95%</t>
+          <t>61,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>75,3%</t>
+          <t>74,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>140174</t>
+          <t>143228</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>187278</t>
+          <t>185696</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>37,95%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>251343</t>
+          <t>249947</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>275720</t>
+          <t>273443</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>84,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>47898</t>
+          <t>48983</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>75741</t>
+          <t>75422</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>38,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>302008</t>
+          <t>303590</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>349112</t>
+          <t>346058</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>61,72%</t>
+          <t>62,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>71,35%</t>
+          <t>70,73%</t>
         </is>
       </c>
     </row>
@@ -3708,12 +3708,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28950</t>
+          <t>29520</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>55108</t>
+          <t>55751</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>179893</t>
+          <t>178418</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>207274</t>
+          <t>205829</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>71,16%</t>
+          <t>70,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>81,99%</t>
+          <t>81,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>210279</t>
+          <t>209223</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>260355</t>
+          <t>261439</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>33,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>42,23%</t>
+          <t>42,4%</t>
         </is>
       </c>
     </row>
@@ -3821,12 +3821,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>308662</t>
+          <t>308019</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>334820</t>
+          <t>334250</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>84,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>45521</t>
+          <t>46966</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>72902</t>
+          <t>74377</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>356211</t>
+          <t>355127</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>406287</t>
+          <t>407343</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>57,77%</t>
+          <t>57,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>65,9%</t>
+          <t>66,07%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>148641</t>
+          <t>148660</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>200744</t>
+          <t>199512</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>594825</t>
+          <t>595942</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>651059</t>
+          <t>654384</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>64,75%</t>
+          <t>64,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>70,87%</t>
+          <t>71,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>750687</t>
+          <t>753662</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>845000</t>
+          <t>847521</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>36,94%</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1174605</t>
+          <t>1175837</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1226708</t>
+          <t>1226689</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>267632</t>
+          <t>264307</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>323866</t>
+          <t>322749</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1449040</t>
+          <t>1446519</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1543353</t>
+          <t>1540378</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>63,17%</t>
+          <t>63,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>67,15%</t>
         </is>
       </c>
     </row>
@@ -4431,7 +4431,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su pareja percibe algún tipo de pensión en 2016</t>
+          <t>Población según si su pareja percibe algún tipo de pensión en 2016 (tasa de respuesta: 94,82%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4626,12 +4626,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23793</t>
+          <t>22725</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>44379</t>
+          <t>43959</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4661,12 +4661,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>122649</t>
+          <t>121911</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>149077</t>
+          <t>147905</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>60,46%</t>
+          <t>60,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>72,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>147299</t>
+          <t>146296</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>189382</t>
+          <t>189813</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4711,12 +4711,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>38,9%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>240701</t>
+          <t>241121</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>261287</t>
+          <t>262355</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>84,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>53790</t>
+          <t>54962</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>80218</t>
+          <t>80956</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>39,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>298566</t>
+          <t>298135</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>340649</t>
+          <t>341652</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>61,19%</t>
+          <t>61,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>69,81%</t>
+          <t>70,02%</t>
         </is>
       </c>
     </row>
@@ -4969,12 +4969,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40131</t>
+          <t>39701</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>69350</t>
+          <t>68411</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4984,12 +4984,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>163000</t>
+          <t>162709</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>196887</t>
+          <t>195143</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5019,12 +5019,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>58,17%</t>
+          <t>58,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>70,27%</t>
+          <t>69,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>208474</t>
+          <t>204925</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>259043</t>
+          <t>257074</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5054,12 +5054,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>38,06%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>325908</t>
+          <t>326847</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>355127</t>
+          <t>355557</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,45%</t>
+          <t>82,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>83304</t>
+          <t>85048</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>117191</t>
+          <t>117482</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>41,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>416406</t>
+          <t>418375</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>466975</t>
+          <t>470524</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,65%</t>
+          <t>61,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,14%</t>
+          <t>69,66%</t>
         </is>
       </c>
     </row>
@@ -5312,12 +5312,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16527</t>
+          <t>16817</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>37158</t>
+          <t>36909</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5327,12 +5327,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>110463</t>
+          <t>110876</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>136900</t>
+          <t>137436</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5362,12 +5362,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>56,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>69,37%</t>
+          <t>69,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>128905</t>
+          <t>128705</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>170885</t>
+          <t>171116</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5397,12 +5397,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>33,18%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>281189</t>
+          <t>281438</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>301820</t>
+          <t>301530</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>60450</t>
+          <t>59914</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>86887</t>
+          <t>86474</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>43,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>344812</t>
+          <t>344581</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>386792</t>
+          <t>386992</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,86%</t>
+          <t>66,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>75,04%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>46121</t>
+          <t>46510</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>72485</t>
+          <t>73795</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>138054</t>
+          <t>138576</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>165703</t>
+          <t>165933</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>63,92%</t>
+          <t>64,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>76,72%</t>
+          <t>76,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>187097</t>
+          <t>187612</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>233742</t>
+          <t>233880</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>40,66%</t>
         </is>
       </c>
     </row>
@@ -5768,12 +5768,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>286669</t>
+          <t>285359</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>313033</t>
+          <t>312644</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5783,12 +5783,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>79,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>87,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>50286</t>
+          <t>50056</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>77935</t>
+          <t>77413</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>35,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>341400</t>
+          <t>341262</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>388045</t>
+          <t>387530</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>59,36%</t>
+          <t>59,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,47%</t>
+          <t>67,38%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>145447</t>
+          <t>147024</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>194464</t>
+          <t>194003</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>561515</t>
+          <t>564336</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>621681</t>
+          <t>621389</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>62,64%</t>
+          <t>62,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>69,35%</t>
+          <t>69,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>718371</t>
+          <t>720959</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>813686</t>
+          <t>811145</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>35,98%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1163375</t>
+          <t>1163836</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1212392</t>
+          <t>1210815</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>274716</t>
+          <t>275008</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>334882</t>
+          <t>332061</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>37,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1440551</t>
+          <t>1443092</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1535866</t>
+          <t>1533278</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>63,9%</t>
+          <t>64,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,13%</t>
+          <t>68,02%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P74B-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P74B-Habitat-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20246</t>
+          <t>20022</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>40541</t>
+          <t>40692</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>114532</t>
+          <t>113670</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>131087</t>
+          <t>130534</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>78,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>134684</t>
+          <t>132797</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>174844</t>
+          <t>174779</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>37,17%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>284604</t>
+          <t>284453</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>304899</t>
+          <t>305123</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>87,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14028</t>
+          <t>14581</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30583</t>
+          <t>31445</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>295416</t>
+          <t>295481</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>335576</t>
+          <t>337463</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>62,82%</t>
+          <t>62,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>71,76%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25409</t>
+          <t>25062</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>48290</t>
+          <t>50537</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>131506</t>
+          <t>131673</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>150412</t>
+          <t>150741</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>79,25%</t>
+          <t>79,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>154964</t>
+          <t>153576</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>199332</t>
+          <t>200204</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>33,41%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>384930</t>
+          <t>382683</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>407811</t>
+          <t>408158</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>15531</t>
+          <t>15202</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>34437</t>
+          <t>34270</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>399831</t>
+          <t>398959</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>444199</t>
+          <t>445587</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,73%</t>
+          <t>66,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,14%</t>
+          <t>74,37%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9188</t>
+          <t>9397</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25823</t>
+          <t>24862</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>87329</t>
+          <t>87715</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>104462</t>
+          <t>104556</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>71,75%</t>
+          <t>72,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>85,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>95359</t>
+          <t>95664</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>130561</t>
+          <t>132056</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>30,17%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>290232</t>
+          <t>291193</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>306867</t>
+          <t>306658</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17249</t>
+          <t>17155</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>34382</t>
+          <t>33996</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>307205</t>
+          <t>305710</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>342407</t>
+          <t>342102</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>70,18%</t>
+          <t>69,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>78,15%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18572</t>
+          <t>19110</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37826</t>
+          <t>38899</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>133937</t>
+          <t>132449</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>154323</t>
+          <t>154623</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>74,7%</t>
+          <t>73,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>150148</t>
+          <t>151101</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>191879</t>
+          <t>193820</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>37,24%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>303265</t>
+          <t>302192</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>322519</t>
+          <t>321981</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>24985</t>
+          <t>24685</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>45371</t>
+          <t>46859</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>328520</t>
+          <t>326579</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>370251</t>
+          <t>369298</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,13%</t>
+          <t>62,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>70,96%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>87341</t>
+          <t>88479</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>128270</t>
+          <t>128871</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>487602</t>
+          <t>486902</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>524709</t>
+          <t>525540</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>79,66%</t>
+          <t>79,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>85,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>573623</t>
+          <t>573265</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>658317</t>
+          <t>654471</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>32,28%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1287242</t>
+          <t>1286641</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1328171</t>
+          <t>1327033</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>87367</t>
+          <t>86536</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>124474</t>
+          <t>125174</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1369271</t>
+          <t>1373117</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1453965</t>
+          <t>1454323</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,53%</t>
+          <t>67,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>71,73%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>35222</t>
+          <t>35245</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>62037</t>
+          <t>61545</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>102792</t>
+          <t>101805</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>129761</t>
+          <t>130897</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>53,11%</t>
+          <t>52,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>67,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>142285</t>
+          <t>144439</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>187982</t>
+          <t>185837</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>37,6%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>238660</t>
+          <t>239152</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>265475</t>
+          <t>265452</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,37%</t>
+          <t>79,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>63783</t>
+          <t>62647</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>90752</t>
+          <t>91739</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>46,89%</t>
+          <t>47,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>306260</t>
+          <t>308405</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>351957</t>
+          <t>349803</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>61,97%</t>
+          <t>62,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>70,78%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>38803</t>
+          <t>39295</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>68013</t>
+          <t>68579</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>165514</t>
+          <t>164360</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>199179</t>
+          <t>198963</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>59,45%</t>
+          <t>59,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>71,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>210108</t>
+          <t>209675</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>261281</t>
+          <t>261302</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,7 +3107,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>347521</t>
+          <t>346955</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>376731</t>
+          <t>376239</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>83,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>79235</t>
+          <t>79451</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>112900</t>
+          <t>114054</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>432667</t>
+          <t>432646</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>483840</t>
+          <t>484273</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3225,7 +3225,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,72%</t>
+          <t>69,79%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21904</t>
+          <t>21218</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>45400</t>
+          <t>45837</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>118516</t>
+          <t>118631</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>144955</t>
+          <t>146006</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>61,11%</t>
+          <t>61,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>74,74%</t>
+          <t>75,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>143228</t>
+          <t>141748</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>185696</t>
+          <t>186302</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>38,08%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>249947</t>
+          <t>249510</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>273443</t>
+          <t>274129</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,63%</t>
+          <t>84,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>48983</t>
+          <t>47932</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>75422</t>
+          <t>75307</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>303590</t>
+          <t>302984</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>346058</t>
+          <t>347538</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>62,05%</t>
+          <t>61,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>70,73%</t>
+          <t>71,03%</t>
         </is>
       </c>
     </row>
@@ -3708,12 +3708,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29520</t>
+          <t>29101</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>55751</t>
+          <t>55032</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>178418</t>
+          <t>178972</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>205829</t>
+          <t>206148</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>70,58%</t>
+          <t>70,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>81,42%</t>
+          <t>81,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>209223</t>
+          <t>211660</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>261439</t>
+          <t>262077</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>42,51%</t>
         </is>
       </c>
     </row>
@@ -3821,12 +3821,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>308019</t>
+          <t>308738</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>334250</t>
+          <t>334669</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>46966</t>
+          <t>46647</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>74377</t>
+          <t>73823</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>355127</t>
+          <t>354489</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>407343</t>
+          <t>404906</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>57,6%</t>
+          <t>57,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,07%</t>
+          <t>65,67%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>148660</t>
+          <t>147863</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>199512</t>
+          <t>200353</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>595942</t>
+          <t>596811</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>654384</t>
+          <t>652904</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>64,87%</t>
+          <t>64,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>71,23%</t>
+          <t>71,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>753662</t>
+          <t>752333</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>847521</t>
+          <t>845417</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>36,85%</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1175837</t>
+          <t>1174996</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1226689</t>
+          <t>1227486</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>85,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>264307</t>
+          <t>265787</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>322749</t>
+          <t>321880</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>35,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1446519</t>
+          <t>1448623</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1540378</t>
+          <t>1541707</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>63,06%</t>
+          <t>63,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>67,15%</t>
+          <t>67,2%</t>
         </is>
       </c>
     </row>
@@ -4626,12 +4626,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22725</t>
+          <t>23391</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43959</t>
+          <t>43720</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4661,12 +4661,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>121911</t>
+          <t>121259</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>147905</t>
+          <t>148985</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>59,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>72,91%</t>
+          <t>73,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>146296</t>
+          <t>146578</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>189813</t>
+          <t>188200</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4711,12 +4711,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>38,57%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>241121</t>
+          <t>241360</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>262355</t>
+          <t>261689</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,58%</t>
+          <t>84,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>54962</t>
+          <t>53882</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>80956</t>
+          <t>81608</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>40,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>298135</t>
+          <t>299748</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>341652</t>
+          <t>341370</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>61,1%</t>
+          <t>61,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>70,02%</t>
+          <t>69,96%</t>
         </is>
       </c>
     </row>
@@ -4969,12 +4969,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>39701</t>
+          <t>40411</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>68411</t>
+          <t>67916</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4984,12 +4984,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>162709</t>
+          <t>163992</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>195143</t>
+          <t>197972</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5019,12 +5019,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>58,07%</t>
+          <t>58,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>69,65%</t>
+          <t>70,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>204925</t>
+          <t>208189</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>257074</t>
+          <t>257561</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5054,12 +5054,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>38,13%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>326847</t>
+          <t>327342</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>355557</t>
+          <t>354847</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,69%</t>
+          <t>82,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>89,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>85048</t>
+          <t>82219</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>117482</t>
+          <t>116199</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>41,93%</t>
+          <t>41,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>418375</t>
+          <t>417888</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>470524</t>
+          <t>467260</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,94%</t>
+          <t>61,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,66%</t>
+          <t>69,18%</t>
         </is>
       </c>
     </row>
@@ -5312,12 +5312,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16817</t>
+          <t>17112</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36909</t>
+          <t>36355</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5327,12 +5327,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>110876</t>
+          <t>109991</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>137436</t>
+          <t>138187</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5362,12 +5362,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>56,18%</t>
+          <t>55,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>69,64%</t>
+          <t>70,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>128705</t>
+          <t>127678</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>171116</t>
+          <t>170695</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5397,12 +5397,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>33,1%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>281438</t>
+          <t>281992</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>301530</t>
+          <t>301235</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>59914</t>
+          <t>59163</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>86474</t>
+          <t>87359</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>43,82%</t>
+          <t>44,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>344581</t>
+          <t>345002</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>386992</t>
+          <t>388019</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,82%</t>
+          <t>66,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>75,04%</t>
+          <t>75,24%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>46510</t>
+          <t>45498</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>73795</t>
+          <t>71884</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>138576</t>
+          <t>138661</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>165933</t>
+          <t>166199</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>64,16%</t>
+          <t>64,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>76,82%</t>
+          <t>76,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>187612</t>
+          <t>188381</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>233880</t>
+          <t>235972</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>41,03%</t>
         </is>
       </c>
     </row>
@@ -5768,12 +5768,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>285359</t>
+          <t>287270</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>312644</t>
+          <t>313656</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5783,12 +5783,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,45%</t>
+          <t>79,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,05%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>50056</t>
+          <t>49790</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>77413</t>
+          <t>77328</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>35,84%</t>
+          <t>35,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>341262</t>
+          <t>339170</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>387530</t>
+          <t>386761</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>59,34%</t>
+          <t>58,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,38%</t>
+          <t>67,25%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>147024</t>
+          <t>146154</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>194003</t>
+          <t>195350</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>564336</t>
+          <t>563374</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>621389</t>
+          <t>623986</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>62,96%</t>
+          <t>62,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>69,32%</t>
+          <t>69,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>720959</t>
+          <t>715239</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>811145</t>
+          <t>803734</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>35,65%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1163836</t>
+          <t>1162489</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1210815</t>
+          <t>1211685</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,71%</t>
+          <t>85,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,17%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>275008</t>
+          <t>272411</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>332061</t>
+          <t>333023</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>37,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1443092</t>
+          <t>1450503</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1533278</t>
+          <t>1538998</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,02%</t>
+          <t>64,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,02%</t>
+          <t>68,27%</t>
         </is>
       </c>
     </row>
